--- a/vimeo_links_omit.xlsx
+++ b/vimeo_links_omit.xlsx
@@ -1,40 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="8160" yWindow="900" windowWidth="12435" windowHeight="12075" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Vimeo Links" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vimeo Links" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="6"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,7 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
       </patternFill>
     </fill>
     <fill>
@@ -64,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -87,9 +110,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -452,8 +490,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F106"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -463,7 +501,7 @@
     <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>講師名（英語）</t>
@@ -495,7 +533,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="27" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -523,11 +561,11 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1154202805</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>https://vimeo.com/1154200765</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -555,11 +593,11 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1154202922</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>https://vimeo.com/1154200948</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -591,7 +629,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="27" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -619,11 +657,11 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1154203273</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>https://vimeo.com/1154203167</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -644,14 +682,14 @@
           <t>Trauma-Informed Care</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1154203273</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>https://vimeo.com/1154203167</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -683,7 +721,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="27" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -715,7 +753,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -747,7 +785,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -779,7 +817,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="54" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -811,7 +849,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="54" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -843,7 +881,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -875,7 +913,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="54" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -907,7 +945,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="54" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -1099,7 +1137,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="27" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Fukashi Udaka</t>
@@ -1163,7 +1201,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="27" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Fukashi Udaka</t>
@@ -1195,7 +1233,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="27" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Sho Furuta</t>
@@ -1227,7 +1265,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="27" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Sho Furuta</t>
@@ -1259,7 +1297,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="27" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Sho Furuta</t>
@@ -1291,7 +1329,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="27" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Sho Furuta</t>
@@ -1323,7 +1361,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="27" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Sho Furuta</t>
@@ -1355,7 +1393,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="40.5" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1387,7 +1425,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="40.5" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1419,7 +1457,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="40.5" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1451,7 +1489,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="40.5" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1483,7 +1521,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="40.5" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1515,7 +1553,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="40.5" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1547,7 +1585,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="40.5" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1739,7 +1777,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="27" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Dr.Junji Machi</t>
@@ -1771,7 +1809,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="27" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Dr.Junji Machi</t>
@@ -1803,7 +1841,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="27" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Dr.Junji Machi</t>
@@ -1835,7 +1873,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="27" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Dr.Jannet Lee Jayaram</t>
@@ -1867,7 +1905,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="27" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Dr.Jannet Lee Jayaram</t>
@@ -1899,7 +1937,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="27" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Dr.Jannet Lee Jayaram</t>
@@ -1931,7 +1969,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="27" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Dr.Jannet Lee Jayaram</t>
@@ -1963,7 +2001,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="27" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Dr.Jannet Lee Jayaram</t>
@@ -1995,7 +2033,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="27" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Dr.Jannet Lee Jayaram</t>
@@ -2027,7 +2065,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="27" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Dr. Taro Shimizu</t>
@@ -2055,11 +2093,11 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1192449734</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
+          <t>https://vimeo.com/1177162061</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="27" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Dr. Taro Shimizu</t>
@@ -2087,11 +2125,11 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1192449909</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
+          <t>https://vimeo.com/1177162237</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="27" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Dr. Taro Shimizu</t>
@@ -2119,11 +2157,11 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1192450070</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
+          <t>https://vimeo.com/1177162517</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="27" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
           <t>Dr. Taro Shimizu</t>
@@ -2151,11 +2189,11 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1192450190</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
+          <t>https://vimeo.com/1177162727</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40.5" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2187,7 +2225,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="40.5" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2219,7 +2257,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="40.5" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2251,7 +2289,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="40.5" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2283,7 +2321,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="40.5" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2315,7 +2353,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="40.5" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2347,7 +2385,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="40.5" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2379,7 +2417,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="40.5" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2411,7 +2449,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="27" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2443,7 +2481,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="27" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2475,7 +2513,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="27" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2507,7 +2545,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="27" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2539,7 +2577,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="27" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2571,7 +2609,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="27" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2603,7 +2641,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="27" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2635,7 +2673,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="27" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2667,7 +2705,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="27" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2699,7 +2737,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="54" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
           <t>Dr. Shin Miyata</t>
@@ -2731,7 +2769,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="54" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Dr. Shin Miyata</t>
@@ -2763,7 +2801,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="54" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Dr. Shin Miyata</t>
@@ -2795,7 +2833,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="54" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Dr. Shin Miyata</t>
@@ -2827,7 +2865,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="54" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
           <t>Dr. Shin Miyata</t>
@@ -2859,7 +2897,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="54" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Dr. Kana Miyata</t>
@@ -2872,7 +2910,8 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Associate Professor Pediatric General and Thoracic Surgery, SSM Health Cardinal Glennon Children's Hospital St.Louis University School of Medicine</t>
+          <t>Associate Professor  Department of Internal Medicine_x000D_
+         Division of Nephrology, St Louis University School of Medicine</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -2888,6 +2927,966 @@
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>https://vimeo.com/1204027423</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Kazuhito Hirata</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>循環器内科</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>社会福祉法人友愛会 友愛医療センター</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>JVP (Jugular Venous Pressure and Apex Beat)</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>353300</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1214920052</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Kazuhito Hirata</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>循環器内科</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>社会福祉法人友愛会 友愛医療センター</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Auscultation Workshop (Systolic Murmurs)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>687971</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1214919031</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Kazuhito Hirata</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>循環器内科</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>社会福祉法人友愛会 友愛医療センター</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Cardiac Auscultation (S2 and Extra Heart Sounds)</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>353300</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1214919113</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Kazuhito Hirata</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>循環器内科</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>社会福祉法人友愛会 友愛医療センター</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Auscultation Workshop (Extra Heart Sounds and S2)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>687971</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1214919179</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Kazuhito Hirata</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>循環器内科</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>社会福祉法人友愛会 友愛医療センター</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Essential ECG Skills in the ER 1</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>579728</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1214919281</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Kazuhito Hirata</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>循環器内科</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>社会福祉法人友愛会 友愛医療センター</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Don't Miss Occult STEMI!</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>353300</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1214919431</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Kazuhito Hirata</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>循環器内科</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>社会福祉法人友愛会 友愛医療センター</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Auscultation Workshop (Diastolic Murmurs and Friction Rub)</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>687971</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1214919536</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Kazuhito Hirata</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>循環器内科</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>社会福祉法人友愛会 友愛医療センター</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Essential ECG Skills in the ER 2</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>579728</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1214919645</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="40.5" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Richard McCartin</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>産婦人科</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Department of Obstetrics and Gynecology, John A. Burns School of Medicine, University of Hawaii</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Understanding the characteristics of energy devices and their safe use in surgery</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>154785</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1220355023</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="40.5" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Richard McCartin</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>産婦人科</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Department of Obstetrics and Gynecology, John A. Burns School of Medicine, University of Hawaii</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Management of uterine fibroids and endometriosis</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>154785</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1220355173</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="40.5" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Richard McCartin</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>産婦人科</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Department of Obstetrics and Gynecology, John A. Burns School of Medicine, University of Hawaii</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Patient safety</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>154785</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1220355314</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="40.5" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Richard McCartin</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>産婦人科</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Department of Obstetrics and Gynecology, John A. Burns School of Medicine, University of Hawaii</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Management of ovarian cysts</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>154785</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1220355441</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="40.5" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Richard McCartin</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>産婦人科</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Department of Obstetrics and Gynecology, John A. Burns School of Medicine, University of Hawaii</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Recovery After Surgery (ERAS)</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>154785</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1220355502</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="54" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Joel Branch</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>内科</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Director, Internal Medicine. Education &amp; Simulation Skills Training. Shonan Kamakura General Hosp. Director of Clinical Education Yao Tokushukai General Hospital</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Sudden headache in α 52-yaer-old Female with migraine</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>587530</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1224759008</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="54" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Joel Branch</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>内科</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Director, Internal Medicine. Education &amp; Simulation Skills Training. Shonan Kamakura General Hosp. Director of Clinical Education Yao Tokushukai General Hospital</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>61-year-old male, impaired consciousness</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>587530</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1224759201</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="54" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Joel Branch</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>内科</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Director, Internal Medicine. Education &amp; Simulation Skills Training. Shonan Kamakura General Hosp. Director of Clinical Education Yao Tokushukai General Hospital</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Important nail signs</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>300032</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1224759433</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="54" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Joel Branch</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>内科</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Director, Internal Medicine. Education &amp; Simulation Skills Training. Shonan Kamakura General Hosp. Director of Clinical Education Yao Tokushukai General Hospital</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>32-year-old Female with Headache</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>587530</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1224759676</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="54" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Joel Branch</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>内科</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Director, Internal Medicine. Education &amp; Simulation Skills Training. Shonan Kamakura General Hosp. Director of Clinical Education Yao Tokushukai General Hospital</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Why the stethoscope is still an intrinsic tool of a physician</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>300032</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1224759857</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="54" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Joel Branch</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>内科</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Director, Internal Medicine. Education &amp; Simulation Skills Training. Shonan Kamakura General Hosp. Director of Clinical Education Yao Tokushukai General Hospital</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>74-year-old woman with altered behavior and progressive gait disturbance</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>587530</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1224760011</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="54" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Joel Branch</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>内科</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Director, Internal Medicine. Education &amp; Simulation Skills Training. Shonan Kamakura General Hosp. Director of Clinical Education Yao Tokushukai General Hospital</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Treatment Paralysis</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>300032</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1224760583</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="54" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Joel Branch</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>内科</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Director, Internal Medicine. Education &amp; Simulation Skills Training. Shonan Kamakura General Hosp. Director of Clinical Education Yao Tokushukai General Hospital</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>74-year-old man, dyspnea with chest pain</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>587530</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1224760864</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>Dr.Amteshwar Singh</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>内科コンサルタント</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>Physical Examination-The Why, The How, and The New Tools</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>245387</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1235238237</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>Dr.Amteshwar Singh</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>内科コンサルタント</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Neurologic Examination in a patient with left sided weakness</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>313180</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1235238485</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>Dr.Amteshwar Singh</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>内科コンサルタント</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>Isolated Nystagmus and Ataxia – Neurologic</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>245387</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1235238729</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>Dr.Amteshwar Singh</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>内科コンサルタント</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>Painful Weakness and Edema of the Legs – Neuromuscular Examination</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>245387</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1235239059</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>Dr.Amteshwar Singh</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>内科コンサルタント</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>Examining joints in a patient with acute monoarticular swelling</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>313180</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1235239404</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>Dr.Amteshwar Singh</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>内科コンサルタント</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Adult-Onset Chorea in a geriatric patient – Neurologic</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>245387</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1235239662</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>Dr.Amteshwar Singh</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>内科コンサルタント</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>Examining the heart in a patient with dyspnea on exertion and pedal edema</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>313180</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1235239924</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>Dr.Amteshwar Singh</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>内科コンサルタント</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>Unresolving pneumonia needing a diagnostic time out</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>245387</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1235240131</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>Dr.Amteshwar Singh</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>内科コンサルタント</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>Respiratory Examination in a Dyspneic patient</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>313180</t>
+        </is>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1235240362</t>
         </is>
       </c>
     </row>
@@ -2968,7 +3967,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/vimeo_links_omit.xlsx
+++ b/vimeo_links_omit.xlsx
@@ -2,57 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="8160" yWindow="900" windowWidth="12435" windowHeight="12075" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vimeo Links" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <color rgb="FF0563C1"/>
-      <sz val="11"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <sz val="6"/>
-      <scheme val="minor"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -61,12 +43,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCE6F1"/>
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,24 +87,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -490,8 +452,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
+  <dimension ref="A1:F109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -501,7 +463,7 @@
     <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>講師名（英語）</t>
@@ -533,7 +495,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="27" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -561,11 +523,11 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1154200765</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="27" customHeight="1">
+          <t>https://vimeo.com/1154202805</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -593,11 +555,11 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1154200948</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="27" customHeight="1">
+          <t>https://vimeo.com/1154202922</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -629,7 +591,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="27" customHeight="1">
+    <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -657,11 +619,11 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1154203167</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="27" customHeight="1">
+          <t>https://vimeo.com/1154203273</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -682,14 +644,14 @@
           <t>Trauma-Informed Care</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1154203167</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="27" customHeight="1">
+          <t>https://vimeo.com/1154203273</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -721,7 +683,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="27" customHeight="1">
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Dr. Michele Pangilinan</t>
@@ -753,7 +715,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -785,7 +747,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1">
+    <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -817,7 +779,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="54" customHeight="1">
+    <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -849,7 +811,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="54" customHeight="1">
+    <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -881,7 +843,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="54" customHeight="1">
+    <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -913,7 +875,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1">
+    <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -945,7 +907,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
+    <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Dr.Joel Branch</t>
@@ -1137,7 +1099,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="27" customHeight="1">
+    <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Fukashi Udaka</t>
@@ -1201,7 +1163,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="27" customHeight="1">
+    <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Fukashi Udaka</t>
@@ -1233,7 +1195,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="27" customHeight="1">
+    <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Sho Furuta</t>
@@ -1265,7 +1227,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="27" customHeight="1">
+    <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Sho Furuta</t>
@@ -1297,7 +1259,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="27" customHeight="1">
+    <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Sho Furuta</t>
@@ -1329,7 +1291,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="27" customHeight="1">
+    <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Sho Furuta</t>
@@ -1361,7 +1323,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="27" customHeight="1">
+    <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Sho Furuta</t>
@@ -1393,7 +1355,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="40.5" customHeight="1">
+    <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1425,7 +1387,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="40.5" customHeight="1">
+    <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1457,7 +1419,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="40.5" customHeight="1">
+    <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1489,7 +1451,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="40.5" customHeight="1">
+    <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1521,7 +1483,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="40.5" customHeight="1">
+    <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1553,7 +1515,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="40.5" customHeight="1">
+    <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1585,7 +1547,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="40.5" customHeight="1">
+    <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Dr.Scotto K. Kuwada</t>
@@ -1777,7 +1739,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="27" customHeight="1">
+    <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Dr.Junji Machi</t>
@@ -1809,7 +1771,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="27" customHeight="1">
+    <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Dr.Junji Machi</t>
@@ -1841,7 +1803,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="27" customHeight="1">
+    <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Dr.Junji Machi</t>
@@ -1873,7 +1835,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="27" customHeight="1">
+    <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Dr.Jannet Lee Jayaram</t>
@@ -1905,7 +1867,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="27" customHeight="1">
+    <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Dr.Jannet Lee Jayaram</t>
@@ -1937,7 +1899,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="27" customHeight="1">
+    <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Dr.Jannet Lee Jayaram</t>
@@ -1969,7 +1931,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="27" customHeight="1">
+    <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Dr.Jannet Lee Jayaram</t>
@@ -2001,7 +1963,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="27" customHeight="1">
+    <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Dr.Jannet Lee Jayaram</t>
@@ -2033,7 +1995,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="27" customHeight="1">
+    <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Dr.Jannet Lee Jayaram</t>
@@ -2065,7 +2027,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="27" customHeight="1">
+    <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Dr. Taro Shimizu</t>
@@ -2093,11 +2055,11 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1177162061</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="27" customHeight="1">
+          <t>https://vimeo.com/1192449734</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Dr. Taro Shimizu</t>
@@ -2125,11 +2087,11 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1177162237</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="27" customHeight="1">
+          <t>https://vimeo.com/1192449909</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Dr. Taro Shimizu</t>
@@ -2157,11 +2119,11 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1177162517</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="27" customHeight="1">
+          <t>https://vimeo.com/1192450070</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
           <t>Dr. Taro Shimizu</t>
@@ -2189,11 +2151,11 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1177162727</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="40.5" customHeight="1">
+          <t>https://vimeo.com/1192450190</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2225,7 +2187,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="40.5" customHeight="1">
+    <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2257,7 +2219,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="40.5" customHeight="1">
+    <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2289,7 +2251,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="40.5" customHeight="1">
+    <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2321,7 +2283,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="40.5" customHeight="1">
+    <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2353,7 +2315,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="40.5" customHeight="1">
+    <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2385,7 +2347,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="40.5" customHeight="1">
+    <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2417,7 +2379,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="40.5" customHeight="1">
+    <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Dr. Neal A. Palafox</t>
@@ -2449,7 +2411,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="27" customHeight="1">
+    <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2481,7 +2443,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="27" customHeight="1">
+    <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2513,7 +2475,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="27" customHeight="1">
+    <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2545,7 +2507,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="27" customHeight="1">
+    <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2577,7 +2539,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="27" customHeight="1">
+    <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2609,7 +2571,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="27" customHeight="1">
+    <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2641,7 +2603,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="27" customHeight="1">
+    <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2669,11 +2631,11 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1204027316</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="27" customHeight="1">
+          <t>https://vimeo.com/1200665260</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2705,7 +2667,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="27" customHeight="1">
+    <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Dr. Kuo Chiang Lian</t>
@@ -2737,7 +2699,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="54" customHeight="1">
+    <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
           <t>Dr. Shin Miyata</t>
@@ -2769,7 +2731,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="54" customHeight="1">
+    <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Dr. Shin Miyata</t>
@@ -2801,7 +2763,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="54" customHeight="1">
+    <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Dr. Shin Miyata</t>
@@ -2833,7 +2795,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="54" customHeight="1">
+    <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Dr. Shin Miyata</t>
@@ -2865,7 +2827,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="54" customHeight="1">
+    <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
           <t>Dr. Shin Miyata</t>
@@ -2897,7 +2859,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="54" customHeight="1">
+    <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Dr. Kana Miyata</t>
@@ -2910,7 +2872,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Associate Professor  Department of Internal Medicine_x000D_
+          <t>Associate Professor  Department of Internal Medicine
          Division of Nephrology, St Louis University School of Medicine</t>
         </is>
       </c>
@@ -3186,7 +3148,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="40.5" customHeight="1">
+    <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
           <t>Dr. Richard McCartin</t>
@@ -3218,7 +3180,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="40.5" customHeight="1">
+    <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Dr. Richard McCartin</t>
@@ -3250,7 +3212,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="40.5" customHeight="1">
+    <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
           <t>Dr. Richard McCartin</t>
@@ -3282,7 +3244,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="40.5" customHeight="1">
+    <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Dr. Richard McCartin</t>
@@ -3314,7 +3276,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="40.5" customHeight="1">
+    <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
           <t>Dr. Richard McCartin</t>
@@ -3346,7 +3308,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="54" customHeight="1">
+    <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Dr. Joel Branch</t>
@@ -3378,7 +3340,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="54" customHeight="1">
+    <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
           <t>Dr. Joel Branch</t>
@@ -3410,7 +3372,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="54" customHeight="1">
+    <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Dr. Joel Branch</t>
@@ -3442,7 +3404,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="54" customHeight="1">
+    <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
           <t>Dr. Joel Branch</t>
@@ -3474,7 +3436,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="54" customHeight="1">
+    <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Dr. Joel Branch</t>
@@ -3506,7 +3468,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="54" customHeight="1">
+    <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
           <t>Dr. Joel Branch</t>
@@ -3538,7 +3500,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="54" customHeight="1">
+    <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Dr. Joel Branch</t>
@@ -3570,7 +3532,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="54" customHeight="1">
+    <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
           <t>Dr. Joel Branch</t>
@@ -3603,44 +3565,44 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Dr.Amteshwar Singh</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>内科コンサルタント</t>
         </is>
       </c>
-      <c r="C98" s="9" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
         </is>
       </c>
-      <c r="D98" s="9" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Physical Examination-The Why, The How, and The New Tools</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>245387</t>
         </is>
       </c>
-      <c r="F98" s="10" t="inlineStr">
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>https://vimeo.com/1235238237</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="11" t="inlineStr">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>Dr.Amteshwar Singh</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>内科コンサルタント</t>
         </is>
@@ -3655,56 +3617,56 @@
           <t>Neurologic Examination in a patient with left sided weakness</t>
         </is>
       </c>
-      <c r="E99" s="11" t="inlineStr">
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>313180</t>
         </is>
       </c>
-      <c r="F99" s="12" t="inlineStr">
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>https://vimeo.com/1235238485</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Dr.Amteshwar Singh</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>内科コンサルタント</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
         </is>
       </c>
-      <c r="D100" s="9" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Isolated Nystagmus and Ataxia – Neurologic</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>245387</t>
         </is>
       </c>
-      <c r="F100" s="10" t="inlineStr">
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>https://vimeo.com/1235238729</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="11" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>Dr.Amteshwar Singh</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>内科コンサルタント</t>
         </is>
@@ -3719,56 +3681,56 @@
           <t>Painful Weakness and Edema of the Legs – Neuromuscular Examination</t>
         </is>
       </c>
-      <c r="E101" s="11" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr">
         <is>
           <t>245387</t>
         </is>
       </c>
-      <c r="F101" s="12" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>https://vimeo.com/1235239059</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Dr.Amteshwar Singh</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>内科コンサルタント</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Examining joints in a patient with acute monoarticular swelling</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>313180</t>
         </is>
       </c>
-      <c r="F102" s="10" t="inlineStr">
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>https://vimeo.com/1235239404</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="inlineStr">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>Dr.Amteshwar Singh</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>内科コンサルタント</t>
         </is>
@@ -3783,56 +3745,56 @@
           <t>Adult-Onset Chorea in a geriatric patient – Neurologic</t>
         </is>
       </c>
-      <c r="E103" s="11" t="inlineStr">
+      <c r="E103" s="5" t="inlineStr">
         <is>
           <t>245387</t>
         </is>
       </c>
-      <c r="F103" s="12" t="inlineStr">
+      <c r="F103" s="7" t="inlineStr">
         <is>
           <t>https://vimeo.com/1235239662</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Dr.Amteshwar Singh</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>内科コンサルタント</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
         </is>
       </c>
-      <c r="D104" s="9" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Examining the heart in a patient with dyspnea on exertion and pedal edema</t>
         </is>
       </c>
-      <c r="E104" s="8" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>313180</t>
         </is>
       </c>
-      <c r="F104" s="10" t="inlineStr">
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>https://vimeo.com/1235239924</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="11" t="inlineStr">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t>Dr.Amteshwar Singh</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr">
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>内科コンサルタント</t>
         </is>
@@ -3847,46 +3809,142 @@
           <t>Unresolving pneumonia needing a diagnostic time out</t>
         </is>
       </c>
-      <c r="E105" s="11" t="inlineStr">
+      <c r="E105" s="5" t="inlineStr">
         <is>
           <t>245387</t>
         </is>
       </c>
-      <c r="F105" s="12" t="inlineStr">
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>https://vimeo.com/1235240131</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Dr.Amteshwar Singh</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>内科コンサルタント</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>Assistant Professor of Medicine, Johns Hopkins University School of Medicine / Director of Education, Division of Hospital Medicine</t>
         </is>
       </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>Respiratory Examination in a Dyspneic patient</t>
         </is>
       </c>
-      <c r="E106" s="8" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>313180</t>
         </is>
       </c>
-      <c r="F106" s="10" t="inlineStr">
+      <c r="F106" s="4" t="inlineStr">
         <is>
           <t>https://vimeo.com/1235240362</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Masanori Tei</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>総合診療科</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>佐久総合病院 院長</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Tips for Discharge Planning (Part 1): How to Proceed with Discharge Coordination</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>251480</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1238617595</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Masanori Tei</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>総合診療科</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>佐久総合病院 院長</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Role Sharing Among Hospitals in the Era of Community-Based Integrated Care</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>970652</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1238617738</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Masanori Tei</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>総合診療科</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>佐久総合病院 院長</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>Tips for Discharge Planning (Part 2): Choosing the Place of Care After Acute Treatment</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>251480</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1238618109</t>
         </is>
       </c>
     </row>
@@ -3997,8 +4055,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/vimeo_links_omit.xlsx
+++ b/vimeo_links_omit.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vimeo Links" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Vimeo Links" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
